--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488206_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488206_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4396</v>
+        <v>4.3778</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9561</v>
+        <v>6.8697</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.5165</v>
+        <v>-2.4919</v>
       </c>
       <c r="G2" t="n">
         <v>3.283</v>
@@ -610,13 +610,13 @@
         <v>2.7793</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0843</v>
+        <v>-0.1461</v>
       </c>
       <c r="T2" t="n">
-        <v>0.873</v>
+        <v>0.7866</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9573</v>
+        <v>-0.9327</v>
       </c>
       <c r="V2" t="n">
         <v>0.3144</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.0866</v>
+        <v>3.4613</v>
       </c>
       <c r="E3" t="n">
-        <v>7.1323</v>
+        <v>6.5562</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.0457</v>
+        <v>-3.095</v>
       </c>
       <c r="G3" t="n">
         <v>4.1608</v>
@@ -688,13 +688,13 @@
         <v>2.4087</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6287</v>
+        <v>0.0034</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3617</v>
+        <v>0.7856</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.733</v>
+        <v>-0.7822</v>
       </c>
       <c r="V3" t="n">
         <v>-1.2589</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. CABALLERO CARPIO</t>
+          <t>L. LÓPEZ CALZADA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9921</v>
+        <v>0.6441</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6075</v>
+        <v>0.6441</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3846</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.0978</v>
+        <v>0.6441</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5188</v>
+        <v>0.6441</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.579</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9768</v>
+        <v>0.6441</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.1427</v>
+        <v>0.6441</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1659</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.121</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6239</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7448</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1117</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1117</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9782</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>1.5843</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6061</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. LÓPEZ CALZADA</t>
+          <t>S. CABALLERO CARPIO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6441</v>
+        <v>0.1162</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6441</v>
+        <v>-0.2191</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.3354</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6441</v>
+        <v>-1.0978</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6441</v>
+        <v>-0.5188</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-0.579</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6441</v>
+        <v>-0.9768</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6441</v>
+        <v>-1.1427</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.1659</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-0.121</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.6239</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.7448</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.1117</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.1117</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.1023</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-0.6554</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. VALVERDE PIZARRO</t>
+          <t>A. MARTINEZ AGUDO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5548</v>
+        <v>-0.3762</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0118</v>
+        <v>0.6041</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.543</v>
+        <v>-0.9802</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8706</v>
+        <v>-2.9228</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0412</v>
+        <v>-1.9057</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8294</v>
+        <v>-1.0171</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0429</v>
+        <v>-0.3384</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0429</v>
+        <v>-0.5884</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.2501</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9136</v>
+        <v>-2.5844</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-1.3173</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8294</v>
+        <v>-1.2671</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3706</v>
+        <v>1.8529</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3706</v>
+        <v>1.8529</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0547</v>
+        <v>0.3793</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0547</v>
+        <v>0.628</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0.2487</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. USAOLA REDONDO</t>
+          <t>J. VALVERDE PIZARRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7365</v>
+        <v>-0.5548</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.09810000000000001</v>
+        <v>-0.0118</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6384</v>
+        <v>-0.543</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.4935</v>
+        <v>-0.8706</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5565</v>
+        <v>-0.0412</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9370000000000001</v>
+        <v>-0.8294</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2664</v>
+        <v>0.0429</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3865</v>
+        <v>0.0429</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6529</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2271</v>
+        <v>-0.9136</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9429999999999999</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2841</v>
+        <v>-0.8294</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3706</v>
+        <v>0.3706</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.3706</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1313</v>
+        <v>-0.0547</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1641</v>
+        <v>-0.0547</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0328</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. MARTINEZ AGUDO</t>
+          <t>A. USAOLA REDONDO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8773</v>
+        <v>-0.6873</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1029</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9802</v>
+        <v>-0.5891999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.9228</v>
+        <v>-1.4935</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.9057</v>
+        <v>-0.5565</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0171</v>
+        <v>-0.9370000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3384</v>
+        <v>-0.2664</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5884</v>
+        <v>0.3865</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2501</v>
+        <v>-0.6529</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.5844</v>
+        <v>-1.2271</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3173</v>
+        <v>-0.9429999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.2671</v>
+        <v>-0.2841</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8529</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8529</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1219</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1269</v>
+        <v>-0.1641</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2487</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3144</v>
+        <v>1.2589</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3144</v>
+        <v>1.2589</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1831</v>
+        <v>-1.1338</v>
       </c>
       <c r="E10" t="n">
         <v>-0.7741</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.409</v>
+        <v>-0.3598</v>
       </c>
       <c r="G10" t="n">
         <v>-1.4223</v>
@@ -1234,13 +1234,13 @@
         <v>0.3706</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1313</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>-0.1641</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0328</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8021</v>
+        <v>-2.0729</v>
       </c>
       <c r="E11" t="n">
         <v>0.995</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.7971</v>
+        <v>-3.0679</v>
       </c>
       <c r="G11" t="n">
         <v>1.7039</v>
@@ -1312,13 +1312,13 @@
         <v>1.297</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4504</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="T11" t="n">
         <v>-0.235</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2154</v>
+        <v>-0.4862</v>
       </c>
       <c r="V11" t="n">
         <v>-1.5733</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.3683</v>
+        <v>-2.1478</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.5428</v>
+        <v>-1.347</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8254</v>
+        <v>-0.8008</v>
       </c>
       <c r="G12" t="n">
         <v>-1.5888</v>
@@ -1390,13 +1390,13 @@
         <v>0.3706</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2236</v>
+        <v>-0.0031</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1094</v>
+        <v>0.0864</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1142</v>
+        <v>-0.0895</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.2528</v>
+        <v>-2.7331</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.9049</v>
+        <v>-2.3605</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3479</v>
+        <v>-0.3726</v>
       </c>
       <c r="G13" t="n">
         <v>-0.6534</v>
@@ -1468,13 +1468,13 @@
         <v>1.1117</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2463</v>
+        <v>-0.7265</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7784</v>
+        <v>-0.2341</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4678</v>
+        <v>-0.4925</v>
       </c>
       <c r="V13" t="n">
         <v>0.3144</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.5102</v>
+        <v>-5.469</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.7677</v>
+        <v>-1.9727</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.7425</v>
+        <v>-3.4963</v>
       </c>
       <c r="G14" t="n">
         <v>-3.4467</v>
@@ -1546,13 +1546,13 @@
         <v>1.6676</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9724</v>
+        <v>0.0687</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2014</v>
+        <v>0.5935</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.771</v>
+        <v>-0.5248</v>
       </c>
       <c r="V14" t="n">
         <v>-2.8321</v>
@@ -1579,16 +1579,16 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-5.556500000000002</v>
+        <v>-5.0093</v>
       </c>
       <c r="E15" t="n">
-        <v>9.904700000000002</v>
+        <v>10.452</v>
       </c>
       <c r="F15" t="n">
-        <v>-15.4611</v>
+        <v>-15.4613</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.1379</v>
+        <v>-2.137900000000001</v>
       </c>
       <c r="H15" t="n">
         <v>-7.282900000000001</v>
@@ -1600,7 +1600,7 @@
         <v>16.2488</v>
       </c>
       <c r="K15" t="n">
-        <v>3.655400000000002</v>
+        <v>3.6554</v>
       </c>
       <c r="L15" t="n">
         <v>12.5934</v>
@@ -1624,13 +1624,13 @@
         <v>13.8966</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.8093</v>
+        <v>-1.2622</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2388</v>
+        <v>2.7857</v>
       </c>
       <c r="U15" t="n">
-        <v>-4.0479</v>
+        <v>-4.047800000000001</v>
       </c>
       <c r="V15" t="n">
         <v>-3.4622</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. TARRES HERNANDEZ</t>
+          <t>A. RODRIGUEZ TORRERO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.0623</v>
+        <v>3.4061</v>
       </c>
       <c r="E16" t="n">
-        <v>3.7442</v>
+        <v>3.2963</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6819</v>
+        <v>0.1097</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5028</v>
+        <v>3.2108</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.6494</v>
+        <v>3.017</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1522</v>
+        <v>0.1938</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5838</v>
+        <v>5.1267</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.4898</v>
+        <v>3.5508</v>
       </c>
       <c r="L16" t="n">
-        <v>2.0736</v>
+        <v>1.5759</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.081</v>
+        <v>-1.916</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1596</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9214</v>
+        <v>-1.3821</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9264</v>
+        <v>-2.0382</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1853</v>
+        <v>-3.891</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1117</v>
+        <v>1.8529</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6887</v>
+        <v>0.9746</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0869</v>
+        <v>0.8018</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3982</v>
+        <v>0.1728</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9444</v>
+        <v>1.2589</v>
       </c>
       <c r="W16" t="n">
         <v>1.2589</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ TORRERO</t>
+          <t>G. TARRES HERNANDEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.0396</v>
+        <v>3.1431</v>
       </c>
       <c r="E17" t="n">
-        <v>3.1984</v>
+        <v>3.8421</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1589</v>
+        <v>-0.699</v>
       </c>
       <c r="G17" t="n">
-        <v>3.2108</v>
+        <v>0.5028</v>
       </c>
       <c r="H17" t="n">
-        <v>3.017</v>
+        <v>-0.6494</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1938</v>
+        <v>1.1522</v>
       </c>
       <c r="J17" t="n">
-        <v>5.1267</v>
+        <v>1.5838</v>
       </c>
       <c r="K17" t="n">
-        <v>3.5508</v>
+        <v>-0.4898</v>
       </c>
       <c r="L17" t="n">
-        <v>1.5759</v>
+        <v>2.0736</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.916</v>
+        <v>-1.081</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5338000000000001</v>
+        <v>-0.1596</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.3821</v>
+        <v>-0.9214</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.0382</v>
+        <v>0.9264</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.891</v>
+        <v>-0.1853</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8529</v>
+        <v>1.1117</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6081</v>
+        <v>0.7694</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7039</v>
+        <v>1.1848</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0958</v>
+        <v>-0.4154</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2589</v>
+        <v>0.9444</v>
       </c>
       <c r="W17" t="n">
         <v>1.2589</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. LATORRE SANCHEZ</t>
+          <t>R. FREIRE DELTIO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.6103</v>
+        <v>2.9596</v>
       </c>
       <c r="E18" t="n">
-        <v>2.926</v>
+        <v>3.1218</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3157</v>
+        <v>-0.1622</v>
       </c>
       <c r="G18" t="n">
-        <v>2.4381</v>
+        <v>1.7732</v>
       </c>
       <c r="H18" t="n">
-        <v>3.8358</v>
+        <v>0.9837</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3977</v>
+        <v>0.7896</v>
       </c>
       <c r="J18" t="n">
-        <v>3.2033</v>
+        <v>3.5508</v>
       </c>
       <c r="K18" t="n">
-        <v>3.8561</v>
+        <v>1.6016</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6529</v>
+        <v>1.9492</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7651</v>
+        <v>-1.7775</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0203</v>
+        <v>-0.618</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7448</v>
+        <v>-1.1596</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1853</v>
+        <v>1.297</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1117</v>
+        <v>1.297</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0132</v>
+        <v>-0.1107</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6491</v>
+        <v>-0.429</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6623</v>
+        <v>0.3183</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. FREIRE DELTIO</t>
+          <t>J. LATORRE SANCHEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.5776</v>
+        <v>2.6446</v>
       </c>
       <c r="E19" t="n">
-        <v>2.7301</v>
+        <v>2.5342</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1525</v>
+        <v>0.1103</v>
       </c>
       <c r="G19" t="n">
-        <v>1.7732</v>
+        <v>2.4381</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9837</v>
+        <v>3.8358</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7896</v>
+        <v>-1.3977</v>
       </c>
       <c r="J19" t="n">
-        <v>3.5508</v>
+        <v>3.2033</v>
       </c>
       <c r="K19" t="n">
-        <v>1.6016</v>
+        <v>3.8561</v>
       </c>
       <c r="L19" t="n">
-        <v>1.9492</v>
+        <v>-0.6529</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.7775</v>
+        <v>-0.7651</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.618</v>
+        <v>-0.0203</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.1596</v>
+        <v>-0.7448</v>
       </c>
       <c r="P19" t="n">
-        <v>1.297</v>
+        <v>0.1853</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R19" t="n">
-        <v>1.297</v>
+        <v>1.1117</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4927</v>
+        <v>0.0211</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8207</v>
+        <v>0.2574</v>
       </c>
       <c r="U19" t="n">
-        <v>0.328</v>
+        <v>-0.2363</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.1651</v>
+        <v>1.9657</v>
       </c>
       <c r="E20" t="n">
-        <v>2.8275</v>
+        <v>3.2193</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6625</v>
+        <v>-1.2536</v>
       </c>
       <c r="G20" t="n">
         <v>-1.2056</v>
@@ -2014,13 +2014,13 @@
         <v>1.297</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3144</v>
+        <v>0.4862</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1604</v>
+        <v>0.5521</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4748</v>
+        <v>-0.0659</v>
       </c>
       <c r="V20" t="n">
         <v>1.5733</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. VIDAL</t>
+          <t>A. ÁLVAREZ RICO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.0808</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2943</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2135</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8198</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>2.3526</v>
+        <v>0.3221</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.5328</v>
+        <v>0.6221</v>
       </c>
       <c r="J21" t="n">
-        <v>2.5449</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>2.5034</v>
+        <v>0.3221</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0415</v>
+        <v>0.6221</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7251</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1508</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.5743</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.297</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2992</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6566</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.9558</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. ÁLVAREZ RICO</t>
+          <t>B. VIDAL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.9308</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9441000000000001</v>
+        <v>1.686</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>-0.7552</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.8198</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3221</v>
+        <v>2.3526</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6221</v>
+        <v>-1.5328</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9441000000000001</v>
+        <v>2.5449</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3221</v>
+        <v>2.5034</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6221</v>
+        <v>0.0415</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>-1.7251</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>-0.1508</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>-1.5743</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-1.297</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>0.1492</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>-0.2649</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>0.4141</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.033</v>
+        <v>0.6698</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8393</v>
+        <v>1.0351</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8063</v>
+        <v>-0.3653</v>
       </c>
       <c r="G23" t="n">
         <v>-0.6651</v>
@@ -2248,13 +2248,13 @@
         <v>1.4823</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3275</v>
+        <v>0.9644</v>
       </c>
       <c r="T23" t="n">
-        <v>0.868</v>
+        <v>1.0639</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5405</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. ALVAREZ RICO</t>
+          <t>M. MURILLO PONS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3364</v>
+        <v>-0.9433</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4344</v>
+        <v>0.0312</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7709</v>
+        <v>-0.9745</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.977</v>
+        <v>-0.0824</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.467</v>
+        <v>-0.213</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.51</v>
+        <v>0.1306</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.4197</v>
+        <v>0.0859</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.1769</v>
+        <v>0.0859</v>
       </c>
       <c r="L24" t="n">
-        <v>0.7572</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.5573</v>
+        <v>-0.1683</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2901</v>
+        <v>-0.2989</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.2671</v>
+        <v>0.1306</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.1117</v>
+        <v>0.3706</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.7411</v>
+        <v>0.3706</v>
       </c>
       <c r="S24" t="n">
-        <v>2.4378</v>
+        <v>0.0274</v>
       </c>
       <c r="T24" t="n">
-        <v>2.3926</v>
+        <v>-0.0547</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0453</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="V24" t="n">
-        <v>0.3144</v>
+        <v>-1.2589</v>
       </c>
       <c r="W24" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>M. MURILLO PONS</t>
+          <t>A. ALVAREZ RICO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.9926</v>
+        <v>-1.3644</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0312</v>
+        <v>-0.6428</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.0237</v>
+        <v>-0.7216</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.0824</v>
+        <v>-1.977</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.213</v>
+        <v>-1.467</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1306</v>
+        <v>-0.51</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0859</v>
+        <v>-0.4197</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0859</v>
+        <v>-1.1769</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>0.7572</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1683</v>
+        <v>-1.5573</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.2989</v>
+        <v>-0.2901</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1306</v>
+        <v>-1.2671</v>
       </c>
       <c r="P25" t="n">
-        <v>0.3706</v>
+        <v>-1.1117</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R25" t="n">
-        <v>0.3706</v>
+        <v>0.7411</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0219</v>
+        <v>1.4099</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0547</v>
+        <v>1.3154</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0328</v>
+        <v>0.0945</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.2589</v>
+        <v>0.3144</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.7207</v>
+        <v>-3.0822</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.6848</v>
+        <v>-1.391</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.0359</v>
+        <v>-1.6912</v>
       </c>
       <c r="G26" t="n">
         <v>-2.3616</v>
@@ -2482,13 +2482,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.2861</v>
+        <v>-0.6476</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.6566</v>
+        <v>-0.3628</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.6294999999999999</v>
+        <v>-0.2848</v>
       </c>
       <c r="V26" t="n">
         <v>-0.6289</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-3.9066</v>
+        <v>-3.7589</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.8234</v>
+        <v>-2.2152</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.0832</v>
+        <v>-1.5437</v>
       </c>
       <c r="G27" t="n">
         <v>-1.2594</v>
@@ -2560,13 +2560,13 @@
         <v>1.6676</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.4238</v>
+        <v>-0.2761</v>
       </c>
       <c r="T27" t="n">
-        <v>0.3756</v>
+        <v>-0.0161</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.7994</v>
+        <v>-0.2599</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>5.556500000000001</v>
+        <v>7.515000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>15.4613</v>
+        <v>15.4611</v>
       </c>
       <c r="F28" t="n">
-        <v>-9.904999999999999</v>
+        <v>-7.946300000000001</v>
       </c>
       <c r="G28" t="n">
         <v>2.137699999999999</v>
@@ -2629,7 +2629,7 @@
         <v>-12.5933</v>
       </c>
       <c r="P28" t="n">
-        <v>-1.8528</v>
+        <v>-1.852799999999999</v>
       </c>
       <c r="Q28" t="n">
         <v>-13.8965</v>
@@ -2638,13 +2638,13 @@
         <v>12.0437</v>
       </c>
       <c r="S28" t="n">
-        <v>1.809200000000001</v>
+        <v>3.7678</v>
       </c>
       <c r="T28" t="n">
-        <v>4.047899999999999</v>
+        <v>4.0479</v>
       </c>
       <c r="U28" t="n">
-        <v>-2.2386</v>
+        <v>-0.28</v>
       </c>
       <c r="V28" t="n">
         <v>3.4621</v>
